--- a/workbook/agent-workbook.xlsx
+++ b/workbook/agent-workbook.xlsx
@@ -470,7 +470,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>The shared workspace every agent (Claude, Muse, any other applier) and the human work through. Agents read this tab first and follow it exactly.</t>
+          <t>The shared workspace every agent (Claude, Grok Bot, any other applier) and the human work through. Agents read this tab first and follow it exactly.</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>[e.g. claude = role finder + inbox listener; muse = applier]. Each agent writes its own name in Owner fields.</t>
+          <t>[e.g. claude = role finder + inbox listener; grok = applier]. Each agent writes its own name in Owner fields.</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Claim before touching any application form. To claim: set State = claimed, Owner = your agent name, Claimed at = now (UTC), then read the row back. If the row changed under you or someone else's name is there, release nothing and pick a different role. Editing a row someone else owns is never allowed.</t>
+          <t>Claim before touching any application form. To claim: set State = claimed, Owner = your agent name, Claimed at = now (UTC), then read the row back. If the row changed under you or someone else's name is there, release nothing and pick a different role. Editing a row someone else owns is never allowed. To release a role you own and haven't applied to: set State = queued and clear Owner and Claimed at, then log it. A queued row never has an Owner.</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>muse</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>muse</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>muse</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>muse</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>muse</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>muse</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
